--- a/v1.2/A2PICO2.v1.2_BOM.xlsx
+++ b/v1.2/A2PICO2.v1.2_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735C1A7D-5406-48D4-936C-B1578888C1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A82A3E-5EDE-4938-972A-3A230AEA196C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,9 +170,6 @@
     <t>1.28mm Gold Deck MicroSD card (TF card) Self bomb SMD SD Card Connectors ROHS</t>
   </si>
   <si>
-    <t>C428492</t>
-  </si>
-  <si>
     <t>SMD</t>
   </si>
   <si>
@@ -297,6 +294,9 @@
   </si>
   <si>
     <t>C4,C5,C6,C7,C8,C9,C10,C11,C13,C16,C17,C18,C19,C22,C23</t>
+  </si>
+  <si>
+    <t>C5352762</t>
   </si>
 </sst>
 </file>
@@ -809,38 +809,38 @@
     </row>
     <row r="2" spans="1:5" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>27</v>
@@ -851,24 +851,24 @@
     </row>
     <row r="5" spans="1:5" ht="20" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
@@ -925,10 +925,10 @@
         <v>17</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="1" customFormat="1" ht="20" customHeight="1">
@@ -940,7 +940,7 @@
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20" customHeight="1">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="13"/>
     </row>
@@ -963,7 +963,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -977,7 +977,7 @@
         <v>27</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -988,30 +988,30 @@
     </row>
     <row r="15" spans="1:5" ht="20" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="20" customHeight="1">
@@ -1019,13 +1019,13 @@
         <v>47</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="20" customHeight="1">
@@ -1033,7 +1033,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
@@ -1047,13 +1047,13 @@
         <v>27</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="20" customHeight="1">
@@ -1061,7 +1061,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4" t="s">
@@ -1070,53 +1070,53 @@
     </row>
     <row r="21" spans="1:4" ht="20" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20" customHeight="1">
       <c r="A22" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C22" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="20" customHeight="1">
       <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="20" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/v1.2/A2PICO2.v1.2_BOM.xlsx
+++ b/v1.2/A2PICO2.v1.2_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A82A3E-5EDE-4938-972A-3A230AEA196C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFD78CA-87AA-44E4-B65D-7797B0575FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -296,7 +296,7 @@
     <t>C4,C5,C6,C7,C8,C9,C10,C11,C13,C16,C17,C18,C19,C22,C23</t>
   </si>
   <si>
-    <t>C5352762</t>
+    <t>C393941</t>
   </si>
 </sst>
 </file>

--- a/v1.2/A2PICO2.v1.2_BOM.xlsx
+++ b/v1.2/A2PICO2.v1.2_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFD78CA-87AA-44E4-B65D-7797B0575FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0CC46B-93BA-4EAF-B50C-85680563046D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="75">
   <si>
     <t>Comment</t>
   </si>
@@ -140,12 +140,6 @@
     <t>SMA(DO-214AC)</t>
   </si>
   <si>
-    <t>C15008</t>
-  </si>
-  <si>
-    <t>1206</t>
-  </si>
-  <si>
     <t>C2480</t>
   </si>
   <si>
@@ -236,9 +230,6 @@
     <t>6.3V 4.7uF 0603</t>
   </si>
   <si>
-    <t>10V 100uF 1206</t>
-  </si>
-  <si>
     <t>16V 100nF 0402</t>
   </si>
   <si>
@@ -246,9 +237,6 @@
   </si>
   <si>
     <t>C3,C12,C14</t>
-  </si>
-  <si>
-    <t>C24</t>
   </si>
   <si>
     <t>U3</t>
@@ -395,7 +383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -431,9 +419,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -784,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="37.26953125" style="2" customWidth="1"/>
@@ -809,44 +794,44 @@
     </row>
     <row r="2" spans="1:5" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>52</v>
+      <c r="D2" s="13" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20" customHeight="1">
@@ -854,269 +839,255 @@
         <v>56</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="20" customHeight="1">
+      <c r="A7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="1" customFormat="1" ht="20" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="1" customFormat="1" ht="20" customHeight="1">
+      <c r="A9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="1" customFormat="1" ht="20" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="20" customHeight="1">
+      <c r="A11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="12"/>
+    </row>
+    <row r="12" spans="1:5" ht="20" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="20" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="20" customHeight="1">
-      <c r="A8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="1" customFormat="1" ht="20" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="1" customFormat="1" ht="20" customHeight="1">
-      <c r="A10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="1" customFormat="1" ht="20" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="4" t="s">
+      <c r="D12" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="20" customHeight="1">
+      <c r="A13" s="3">
+        <v>27</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="20" customHeight="1">
-      <c r="A12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="13"/>
-    </row>
-    <row r="13" spans="1:5" ht="20" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20" customHeight="1">
-      <c r="A14" s="3">
-        <v>27</v>
+      <c r="A14" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="20" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>70</v>
+      <c r="A16" s="3">
+        <v>47</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="20" customHeight="1">
-      <c r="A17" s="3">
-        <v>47</v>
+      <c r="A17" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="20" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>13</v>
+      <c r="A18" s="3">
+        <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="20" customHeight="1">
-      <c r="A19" s="3">
-        <v>27</v>
+      <c r="A19" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="20" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="20" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4" t="s">
-        <v>50</v>
+      <c r="A21" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20" customHeight="1">
-      <c r="A22" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>66</v>
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="20" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>63</v>
+        <v>35</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="20" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/v1.2/A2PICO2.v1.2_BOM.xlsx
+++ b/v1.2/A2PICO2.v1.2_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0CC46B-93BA-4EAF-B50C-85680563046D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B582273-6E47-4B9E-815F-03BB22D09C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,18 +185,12 @@
     <t>C25190</t>
   </si>
   <si>
-    <t>C20625731</t>
-  </si>
-  <si>
     <t>ABM8-272-T3</t>
   </si>
   <si>
     <t>C42411119</t>
   </si>
   <si>
-    <t>12pF</t>
-  </si>
-  <si>
     <t>R1,R2</t>
   </si>
   <si>
@@ -212,9 +206,6 @@
     <t>RP2354B-A2</t>
   </si>
   <si>
-    <t>C1547</t>
-  </si>
-  <si>
     <t>C6848499</t>
   </si>
   <si>
@@ -248,9 +239,6 @@
     <t>SOT-23-6</t>
   </si>
   <si>
-    <t>C22046</t>
-  </si>
-  <si>
     <t>R3</t>
   </si>
   <si>
@@ -285,6 +273,18 @@
   </si>
   <si>
     <t>C393941</t>
+  </si>
+  <si>
+    <t>C55509827</t>
+  </si>
+  <si>
+    <t>C403945</t>
+  </si>
+  <si>
+    <t>18pF</t>
+  </si>
+  <si>
+    <t>C1549</t>
   </si>
 </sst>
 </file>
@@ -794,52 +794,52 @@
     </row>
     <row r="2" spans="1:5" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
@@ -899,7 +899,7 @@
         <v>34</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="1" customFormat="1" ht="20" customHeight="1">
@@ -911,7 +911,7 @@
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20" customHeight="1">
@@ -919,13 +919,13 @@
         <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E11" s="12"/>
     </row>
@@ -934,7 +934,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
@@ -948,7 +948,7 @@
         <v>27</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -962,7 +962,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -973,16 +973,16 @@
     </row>
     <row r="15" spans="1:5" ht="20" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1">
@@ -990,13 +990,13 @@
         <v>47</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="20" customHeight="1">
@@ -1004,7 +1004,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
@@ -1018,7 +1018,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>29</v>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
@@ -1041,28 +1041,28 @@
     </row>
     <row r="20" spans="1:4" ht="20" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="20" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20" customHeight="1">
@@ -1070,7 +1070,7 @@
         <v>37</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>38</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="23" spans="1:4" ht="20" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>35</v>
@@ -1087,7 +1087,7 @@
         <v>21</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/v1.2/A2PICO2.v1.2_BOM.xlsx
+++ b/v1.2/A2PICO2.v1.2_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B582273-6E47-4B9E-815F-03BB22D09C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A36EEEA-6574-4AF4-A9D4-162535B7C8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -275,9 +275,6 @@
     <t>C393941</t>
   </si>
   <si>
-    <t>C55509827</t>
-  </si>
-  <si>
     <t>C403945</t>
   </si>
   <si>
@@ -285,6 +282,9 @@
   </si>
   <si>
     <t>C1549</t>
+  </si>
+  <si>
+    <t>C51939610</t>
   </si>
 </sst>
 </file>
@@ -794,7 +794,7 @@
     </row>
     <row r="2" spans="1:5" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>54</v>
@@ -803,7 +803,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20" customHeight="1">
@@ -1062,7 +1062,7 @@
         <v>58</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20" customHeight="1">
@@ -1087,7 +1087,7 @@
         <v>21</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
